--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136390002</v>
       </c>
       <c r="B6" t="n">
-        <v>92511</v>
+        <v>92514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136390002</v>
       </c>
       <c r="B6" t="n">
-        <v>92514</v>
+        <v>92515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136390002</v>
       </c>
       <c r="B6" t="n">
-        <v>92515</v>
+        <v>92520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136390002</v>
       </c>
       <c r="B6" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1434,57 +1434,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102199609</v>
+        <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>56888</v>
+        <v>92791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100041</v>
+        <v>6031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coronella austriaca</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Laurenti, 1768</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grinddalen 14, Boh</t>
+          <t>Turebacksvägen, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317412</v>
+        <v>317325</v>
       </c>
       <c r="R9" t="n">
-        <v>6458091</v>
+        <v>6458158</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1508,17 +1502,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Skadad men levande, eventuellt skadad av kråka eller skata</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,38 +1534,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102199609</t>
+          <t>https://artportalen.se/Sighting/137001829</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104015491</v>
+        <v>102199609</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>56888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100041</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Laurenti, 1768</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1584,27 +1573,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grinddalen, skogen, Boh</t>
+          <t>Grinddalen 14, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317405</v>
+        <v>317412</v>
       </c>
       <c r="R10" t="n">
-        <v>6458115</v>
+        <v>6458091</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,12 +1614,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-08</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-08</t>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Skadad men levande, eventuellt skadad av kråka eller skata</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,33 +1633,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Björn Larsson, Moa Pettersson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104015491</t>
+          <t>https://artportalen.se/Sighting/102199609</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132783038</v>
+        <v>104015491</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,23 +1694,23 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grinddalen, Boh</t>
+          <t>Grinddalen, skogen, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>317392</v>
+        <v>317405</v>
       </c>
       <c r="R11" t="n">
-        <v>6458107</v>
+        <v>6458115</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,12 +1734,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1762,24 +1754,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Ellen Larsson</t>
+          <t>Björn Larsson, Moa Pettersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132783038</t>
+          <t>https://artportalen.se/Sighting/104015491</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133970214</v>
+        <v>132783038</v>
       </c>
       <c r="B12" t="n">
         <v>57972</v>
@@ -1822,17 +1814,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grinddalen källpåverkad blandskog, Boh</t>
+          <t>Grinddalen, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>317401</v>
+        <v>317392</v>
       </c>
       <c r="R12" t="n">
-        <v>6458102</v>
+        <v>6458107</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,22 +1848,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,22 +1873,22 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Via Ellen Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133970214</t>
+          <t>https://artportalen.se/Sighting/132783038</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133283114</v>
+        <v>133970214</v>
       </c>
       <c r="B13" t="n">
-        <v>56915</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,16 +1896,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100088</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1936,7 +1918,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
@@ -1947,17 +1928,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grinddalen dammen, Boh</t>
+          <t>Grinddalen källpåverkad blandskog, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>317394</v>
+        <v>317401</v>
       </c>
       <c r="R13" t="n">
-        <v>6458070</v>
+        <v>6458102</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1981,17 +1962,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Snoken hade fångat en vanlig groda som tog lite tid att svälja</t>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,14 +1986,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Gammal bevattningsdamm, nästa igenvuxen</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2017,22 +1997,22 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Ellen Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133283114</t>
+          <t>https://artportalen.se/Sighting/133970214</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129729452</v>
+        <v>133283114</v>
       </c>
       <c r="B14" t="n">
-        <v>57947</v>
+        <v>56915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,21 +2020,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102977</v>
+        <v>100088</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2062,6 +2042,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
@@ -2072,17 +2053,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grinddalen, skogen, Boh</t>
+          <t>Grinddalen dammen, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>317405</v>
+        <v>317394</v>
       </c>
       <c r="R14" t="n">
-        <v>6458115</v>
+        <v>6458070</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,12 +2087,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Snoken hade fångat en vanlig groda som tog lite tid att svälja</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,55 +2106,61 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Gammal bevattningsdamm, nästa igenvuxen</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Björn Larsson, Ellen Larsson</t>
+          <t>Via Ellen Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129729452</t>
+          <t>https://artportalen.se/Sighting/133283114</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123245162</v>
+        <v>129729452</v>
       </c>
       <c r="B15" t="n">
-        <v>58388</v>
+        <v>57947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103001</v>
+        <v>102977</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2220,22 +2212,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,44 +2237,44 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Björn Larsson, Ellen Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123245162</t>
+          <t>https://artportalen.se/Sighting/129729452</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123245085</v>
+        <v>123245162</v>
       </c>
       <c r="B16" t="n">
-        <v>58327</v>
+        <v>58388</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2304,7 +2286,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2385,16 +2367,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123245085</t>
+          <t>https://artportalen.se/Sighting/123245162</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>71343303</v>
+        <v>123245085</v>
       </c>
       <c r="B17" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,48 +2384,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grinddalen, Boh</t>
+          <t>Grinddalen, skogen, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>317392</v>
+        <v>317405</v>
       </c>
       <c r="R17" t="n">
-        <v>6458107</v>
+        <v>6458115</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2467,17 +2450,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>två par, två holkar</t>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,27 +2480,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71343303</t>
+          <t>https://artportalen.se/Sighting/123245085</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123245155</v>
+        <v>71343303</v>
       </c>
       <c r="B18" t="n">
-        <v>58636</v>
+        <v>58439</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,49 +2508,48 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grinddalen, skogen, Boh</t>
+          <t>Grinddalen, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>317405</v>
+        <v>317392</v>
       </c>
       <c r="R18" t="n">
-        <v>6458115</v>
+        <v>6458107</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2586,22 +2573,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2018-05-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>två par, två holkar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,27 +2598,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123245155</t>
+          <t>https://artportalen.se/Sighting/71343303</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133282638</v>
+        <v>123245155</v>
       </c>
       <c r="B19" t="n">
-        <v>30293</v>
+        <v>58636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,42 +2626,49 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>200985</v>
+        <v>103044</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Turebacksvägen, Boh</t>
+          <t>Grinddalen, skogen, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
         <v>317405</v>
       </c>
       <c r="R19" t="n">
-        <v>6458184</v>
+        <v>6458115</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2703,17 +2692,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre barrskog med hassel</t>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2722,34 +2716,33 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133282638</t>
+          <t>https://artportalen.se/Sighting/123245155</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>108776338</v>
+        <v>133282638</v>
       </c>
       <c r="B20" t="n">
-        <v>58085</v>
+        <v>30293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2757,41 +2750,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205976</v>
+        <v>200985</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grinddalen, Boh</t>
+          <t>Turebacksvägen, Boh</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317411</v>
+        <v>317405</v>
       </c>
       <c r="R20" t="n">
-        <v>6458143</v>
+        <v>6458184</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2815,12 +2809,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre barrskog med hassel</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,6 +2828,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2840,22 +2840,22 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Via Ellen Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108776338</t>
+          <t>https://artportalen.se/Sighting/133282638</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>71343353</v>
+        <v>108776338</v>
       </c>
       <c r="B21" t="n">
-        <v>58790</v>
+        <v>58085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,25 +2863,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208245</v>
+        <v>205976</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -2892,13 +2891,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>317392</v>
+        <v>317411</v>
       </c>
       <c r="R21" t="n">
-        <v>6458107</v>
+        <v>6458143</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2922,12 +2921,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2018-05-11</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2018-05-11</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2953,16 +2952,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71343353</t>
+          <t>https://artportalen.se/Sighting/108776338</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>70603491</v>
+        <v>71343353</v>
       </c>
       <c r="B22" t="n">
-        <v>58817</v>
+        <v>58790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2970,50 +2969,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äggläggande</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>dammen, Boh</t>
+          <t>Grinddalen, Boh</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>317384</v>
+        <v>317392</v>
       </c>
       <c r="R22" t="n">
-        <v>6458066</v>
+        <v>6458107</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3037,12 +3028,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
+          <t>2018-05-11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
+          <t>2018-05-11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3062,19 +3053,19 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ellen Larsson, Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70603491</t>
+          <t>https://artportalen.se/Sighting/71343353</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>71343372</v>
+        <v>70603491</v>
       </c>
       <c r="B23" t="n">
         <v>58817</v>
@@ -3108,31 +3099,27 @@
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>äggläggande</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grinddalen, Boh</t>
+          <t>dammen, Boh</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317392</v>
+        <v>317384</v>
       </c>
       <c r="R23" t="n">
-        <v>6458107</v>
+        <v>6458066</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3156,12 +3143,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2018-05-11</t>
+          <t>2018-04-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2018-05-11</t>
+          <t>2018-04-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3181,19 +3168,19 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Ellen Larsson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71343372</t>
+          <t>https://artportalen.se/Sighting/70603491</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>107930276</v>
+        <v>71343372</v>
       </c>
       <c r="B24" t="n">
         <v>58817</v>
@@ -3223,14 +3210,10 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>adult</t>
@@ -3239,27 +3222,23 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grinddalen, Boh</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317394</v>
+        <v>317392</v>
       </c>
       <c r="R24" t="n">
-        <v>6458055</v>
+        <v>6458107</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3283,12 +3262,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2018-05-11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2018-05-11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3297,31 +3276,30 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Moa Pettersson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Moa Pettersson, Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107930276</t>
+          <t>https://artportalen.se/Sighting/71343372</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>108776379</v>
+        <v>107930276</v>
       </c>
       <c r="B25" t="n">
         <v>58817</v>
@@ -3349,25 +3327,45 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grinddalen 14, Boh</t>
+          <t>Grinddalen, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>317412</v>
+        <v>317394</v>
       </c>
       <c r="R25" t="n">
-        <v>6458091</v>
+        <v>6458055</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3391,12 +3389,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3412,27 +3410,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Moa Pettersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Moa Pettersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108776379</t>
+          <t>https://artportalen.se/Sighting/107930276</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132240800</v>
+        <v>108776379</v>
       </c>
       <c r="B26" t="n">
-        <v>58839</v>
+        <v>58817</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,41 +3455,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grinddalen, dammen, Boh</t>
+          <t>Grinddalen 14, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>317387</v>
+        <v>317412</v>
       </c>
       <c r="R26" t="n">
-        <v>6458063</v>
+        <v>6458091</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3515,12 +3497,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3536,27 +3518,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Björn Larsson, Moa Pettersson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132240800</t>
+          <t>https://artportalen.se/Sighting/108776379</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>71844315</v>
+        <v>132240800</v>
       </c>
       <c r="B27" t="n">
-        <v>98194</v>
+        <v>58839</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3564,21 +3546,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220686</v>
+        <v>208249</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3586,22 +3568,36 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grinddalen källpåverkad blandskog, Boh</t>
+          <t>Grinddalen, dammen, Boh</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317401</v>
+        <v>317387</v>
       </c>
       <c r="R27" t="n">
-        <v>6458102</v>
+        <v>6458063</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3625,17 +3621,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2018-06-12</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2018-06-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>källpåverkad barrskog</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3644,30 +3635,31 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson, Moa Pettersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71844315</t>
+          <t>https://artportalen.se/Sighting/132240800</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>91604898</v>
+        <v>71844315</v>
       </c>
       <c r="B28" t="n">
         <v>98194</v>
@@ -3697,34 +3689,25 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Grinddalen, skogen, Boh</t>
+          <t>Grinddalen källpåverkad blandskog, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>317405</v>
+        <v>317401</v>
       </c>
       <c r="R28" t="n">
-        <v>6458115</v>
+        <v>6458102</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3748,12 +3731,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2018-06-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>källpåverkad barrskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3762,84 +3750,87 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Källpåverkad barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91604898</t>
+          <t>https://artportalen.se/Sighting/71844315</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>79043750</v>
+        <v>91604898</v>
       </c>
       <c r="B29" t="n">
-        <v>91060</v>
+        <v>98194</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>245628</v>
+        <v>220686</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granbronssopp</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Butyriboletus subappendiculatus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dermek, Lazebn. &amp; J.Veselský) D.Arora &amp; J.L.Frank</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ulvesund grusgropen, Boh</t>
+          <t>Grinddalen, skogen, Boh</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>317422</v>
+        <v>317405</v>
       </c>
       <c r="R29" t="n">
-        <v>6458267</v>
+        <v>6458115</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3863,12 +3854,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2019-07-22</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2019-07-22</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3881,63 +3872,80 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Källpåverkad barrskog</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79043750</t>
+          <t>https://artportalen.se/Sighting/91604898</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>91518474</v>
+        <v>79043750</v>
       </c>
       <c r="B30" t="n">
-        <v>78261</v>
+        <v>91060</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6051522</v>
+        <v>245628</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granbronssopp</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Elaphomyces nemoreus</t>
+          <t>Butyriboletus subappendiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Jeppson &amp; al.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Dermek, Lazebn. &amp; J.Veselský) D.Arora &amp; J.L.Frank</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ekenhof, Boh</t>
+          <t>Ulvesund grusgropen, Boh</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>317430</v>
+        <v>317422</v>
       </c>
       <c r="R30" t="n">
-        <v>6458088</v>
+        <v>6458267</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3961,12 +3969,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2020-11-14</t>
+          <t>2019-07-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2020-11-14</t>
+          <t>2019-07-22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3975,23 +3983,9 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
-      <c r="AP30" t="inlineStr">
-        <is>
-          <t>Göteborg-Herbarium GB</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>EL168-20</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4004,12 +3998,124 @@
           <t>Ellen Larsson</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79043750</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>91518474</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78261</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6051522</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Elaphomyces nemoreus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Jeppson &amp; al.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ekenhof, Boh</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>317430</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6458088</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2020-11-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2020-11-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>Göteborg-Herbarium GB</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>EL168-20</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ellen Larsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ellen Larsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
         <is>
           <t>Svenska tryffelprojektet</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/91518474</t>
         </is>
@@ -4046,6 +4152,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136390002</v>
       </c>
       <c r="B6" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136390002</v>
       </c>
       <c r="B6" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92847</v>
+        <v>92859</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92863</v>
+        <v>92864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1437,7 +1437,7 @@
         <v>137001829</v>
       </c>
       <c r="B9" t="n">
-        <v>92864</v>
+        <v>92867</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
